--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,6 +1106,113 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114877002</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57235</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörträsket, Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>641129</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7174784</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536455</v>
+        <v>119536407</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>79511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641186</v>
+        <v>641282</v>
       </c>
       <c r="R7" t="n">
-        <v>7175004</v>
+        <v>7174997</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119535992</v>
+        <v>119536654</v>
       </c>
       <c r="B8" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641280</v>
+        <v>641233</v>
       </c>
       <c r="R8" t="n">
-        <v>7175016</v>
+        <v>7174855</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536653</v>
+        <v>119536400</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>56271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,38 +1451,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>208255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641240</v>
+        <v>641141</v>
       </c>
       <c r="R9" t="n">
-        <v>7174847</v>
+        <v>7175001</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1514,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1555,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119536407</v>
+        <v>119537249</v>
       </c>
       <c r="B10" t="n">
-        <v>79511</v>
+        <v>77910</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,25 +1567,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1591,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641282</v>
+        <v>641264</v>
       </c>
       <c r="R10" t="n">
-        <v>7174997</v>
+        <v>7174964</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1626,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119537152</v>
+        <v>119536078</v>
       </c>
       <c r="B11" t="n">
-        <v>77458</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,34 +1683,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641266</v>
+        <v>641251</v>
       </c>
       <c r="R11" t="n">
-        <v>7174960</v>
+        <v>7175002</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1738,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1748,7 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1775,7 +1784,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536078</v>
+        <v>119536072</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -1811,7 +1820,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1820,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641251</v>
+        <v>641156</v>
       </c>
       <c r="R12" t="n">
-        <v>7175002</v>
+        <v>7174814</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1855,7 +1864,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1874,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1901,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536077</v>
+        <v>119536310</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>91844</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1904,43 +1913,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641285</v>
+        <v>641273</v>
       </c>
       <c r="R13" t="n">
-        <v>7174995</v>
+        <v>7174938</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1972,7 +1976,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1986,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537249</v>
+        <v>119535963</v>
       </c>
       <c r="B14" t="n">
-        <v>77910</v>
+        <v>90488</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>641264</v>
+        <v>641273</v>
       </c>
       <c r="R14" t="n">
-        <v>7174964</v>
+        <v>7174937</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2084,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119536654</v>
+        <v>119537152</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>77458</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,21 +2141,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2161,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641233</v>
+        <v>641266</v>
       </c>
       <c r="R15" t="n">
-        <v>7174855</v>
+        <v>7174960</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536310</v>
+        <v>119536077</v>
       </c>
       <c r="B16" t="n">
-        <v>91844</v>
+        <v>57310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2245,38 +2249,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>641273</v>
+        <v>641285</v>
       </c>
       <c r="R16" t="n">
-        <v>7174938</v>
+        <v>7174995</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2308,7 +2317,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,7 +2327,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119537056</v>
+        <v>119535992</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
+        <v>79144</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,21 +2370,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>641268</v>
+        <v>641280</v>
       </c>
       <c r="R17" t="n">
-        <v>7174957</v>
+        <v>7175016</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2420,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2430,7 +2439,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119535963</v>
+        <v>119537056</v>
       </c>
       <c r="B18" t="n">
-        <v>90488</v>
+        <v>78171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,21 +2482,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2506,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>641273</v>
+        <v>641268</v>
       </c>
       <c r="R18" t="n">
-        <v>7174937</v>
+        <v>7174957</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2532,7 +2541,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2542,7 +2551,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,10 +2578,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536072</v>
+        <v>119536653</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,39 +2594,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>641156</v>
+        <v>641240</v>
       </c>
       <c r="R19" t="n">
-        <v>7174814</v>
+        <v>7174847</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2649,7 +2653,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2663,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2686,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536400</v>
+        <v>119536455</v>
       </c>
       <c r="B20" t="n">
-        <v>56271</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2702,38 +2706,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208255</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>641141</v>
+        <v>641186</v>
       </c>
       <c r="R20" t="n">
-        <v>7175001</v>
+        <v>7175004</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -2013,10 +2013,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119535963</v>
+        <v>119537152</v>
       </c>
       <c r="B14" t="n">
-        <v>90488</v>
+        <v>77458</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,21 +2029,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>641273</v>
+        <v>641266</v>
       </c>
       <c r="R14" t="n">
-        <v>7174937</v>
+        <v>7174960</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,10 +2125,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537152</v>
+        <v>119535963</v>
       </c>
       <c r="B15" t="n">
-        <v>77458</v>
+        <v>90488</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641266</v>
+        <v>641273</v>
       </c>
       <c r="R15" t="n">
-        <v>7174960</v>
+        <v>7174937</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119536407</v>
+        <v>119536310</v>
       </c>
       <c r="B7" t="n">
-        <v>79511</v>
+        <v>91844</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>641282</v>
+        <v>641273</v>
       </c>
       <c r="R7" t="n">
-        <v>7174997</v>
+        <v>7174938</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119536654</v>
+        <v>119536455</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>641233</v>
+        <v>641186</v>
       </c>
       <c r="R8" t="n">
-        <v>7174855</v>
+        <v>7175004</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119536400</v>
+        <v>119536654</v>
       </c>
       <c r="B9" t="n">
-        <v>56271</v>
+        <v>79607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,42 +1451,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208255</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>641141</v>
+        <v>641233</v>
       </c>
       <c r="R9" t="n">
-        <v>7175001</v>
+        <v>7174855</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1518,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119537249</v>
+        <v>119537056</v>
       </c>
       <c r="B10" t="n">
-        <v>77910</v>
+        <v>78171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,21 +1567,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1595,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>641264</v>
+        <v>641268</v>
       </c>
       <c r="R10" t="n">
-        <v>7174964</v>
+        <v>7174957</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1630,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119536078</v>
+        <v>119537152</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>77458</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,39 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>641251</v>
+        <v>641266</v>
       </c>
       <c r="R11" t="n">
-        <v>7175002</v>
+        <v>7174960</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1747,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1757,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1784,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119536072</v>
+        <v>119536407</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>79511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,43 +1787,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>641156</v>
+        <v>641282</v>
       </c>
       <c r="R12" t="n">
-        <v>7174814</v>
+        <v>7174997</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1864,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1874,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,10 +1887,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119536310</v>
+        <v>119535992</v>
       </c>
       <c r="B13" t="n">
-        <v>91844</v>
+        <v>79144</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1913,25 +1899,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>641273</v>
+        <v>641280</v>
       </c>
       <c r="R13" t="n">
-        <v>7174938</v>
+        <v>7175016</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1976,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1986,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,10 +1999,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537152</v>
+        <v>119536078</v>
       </c>
       <c r="B14" t="n">
-        <v>77458</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,34 +2015,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>641266</v>
+        <v>641251</v>
       </c>
       <c r="R14" t="n">
-        <v>7174960</v>
+        <v>7175002</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2088,7 +2079,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2098,7 +2089,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2125,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119535963</v>
+        <v>119536653</v>
       </c>
       <c r="B15" t="n">
-        <v>90488</v>
+        <v>79607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2141,21 +2132,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,10 +2156,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641273</v>
+        <v>641240</v>
       </c>
       <c r="R15" t="n">
-        <v>7174937</v>
+        <v>7174847</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2200,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2210,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119536077</v>
+        <v>119535963</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>90488</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,39 +2244,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>641285</v>
+        <v>641273</v>
       </c>
       <c r="R16" t="n">
-        <v>7174995</v>
+        <v>7174937</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2317,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2327,7 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119535992</v>
+        <v>119536077</v>
       </c>
       <c r="B17" t="n">
-        <v>79144</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,34 +2356,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>641280</v>
+        <v>641285</v>
       </c>
       <c r="R17" t="n">
-        <v>7175016</v>
+        <v>7174995</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2429,7 +2420,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2439,7 +2430,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2466,10 +2457,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119537056</v>
+        <v>119537249</v>
       </c>
       <c r="B18" t="n">
-        <v>78171</v>
+        <v>77910</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,21 +2473,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2506,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>641268</v>
+        <v>641264</v>
       </c>
       <c r="R18" t="n">
-        <v>7174957</v>
+        <v>7174964</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2541,7 +2532,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2551,7 +2542,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2578,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536653</v>
+        <v>119536072</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,34 +2585,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>641240</v>
+        <v>641156</v>
       </c>
       <c r="R19" t="n">
-        <v>7174847</v>
+        <v>7174814</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2663,7 +2659,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536455</v>
+        <v>119536400</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>56271</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,34 +2702,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>208255</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>641186</v>
+        <v>641141</v>
       </c>
       <c r="R20" t="n">
-        <v>7175004</v>
+        <v>7175001</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2800,6 +2800,120 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122586703</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Vinliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>641428</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7175228</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Greger Thorsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -2805,7 +2805,7 @@
         <v>122586703</v>
       </c>
       <c r="B21" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 37598-2021 artfynd.xlsx
+++ b/artfynd/A 37598-2021 artfynd.xlsx
@@ -2805,7 +2805,7 @@
         <v>122586703</v>
       </c>
       <c r="B21" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
